--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,10 +1106,7 @@
     <t>845: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE/TIME SPECIMEN TAKEN (#63.04-.01)</t>
   </si>
   <si>
-    <t>Chem.LabChem.LabChemSpecimenDateTime
-Chem.LabPanel.LabChemSpecimenDateTime
-Chem.OrderedLabPanel.LabChemSpecimenDateTime
-Chem.PatientLabChem.LabChemSpecimenDateTime</t>
+    <t>Chem.LabChem.LabChemSpecimenDateTime,Chem.LabPanel.LabChemSpecimenDateTime,Chem.OrderedLabPanel.LabChemSpecimenDateTime,Chem.PatientLabChem.LabChemSpecimenDateTime</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1140,10 +1137,7 @@
     <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (#63.04-.03)</t>
   </si>
   <si>
-    <t>Chem.LabChem.LabChemCompleteDateTime
-Chem.LabPanel.LabChemCompleteDateTime
-Chem.OrderedLabPanel.LabChemCompleteDateTime
-Chem.PatientLabChem.LabChemCompleteDateTime</t>
+    <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1567,8 +1561,7 @@
     <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
   </si>
   <si>
-    <t>Chem.LabChem.ShortAccessionNumber
-Chem.PatientLabChem.ShortAccessionNumber</t>
+    <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
   </si>
   <si>
     <t>Observation.device</t>
@@ -2279,7 +2272,7 @@
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="239.078125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="50.07421875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="183.43359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -662,13 +662,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>851: source value from CHEM, HEM, TOX, RIA, SER, etc. - IEN (#63.04-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>851: source value from CHEM, HEM, TOX, RIA, SER, etc. - IEN (#63.04-.001)</t>
   </si>
   <si>
     <t>Observation.identifier.period</t>
@@ -794,6 +794,9 @@
     <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
   </si>
   <si>
+    <t>860: terminologyMaps using VF_DiagnosticReportLabStatus on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.04-.35 &gt; 63.07-10)</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -807,9 +810,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>860: terminologyMaps using VF_DiagnosticReportLabStatus on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.04-.35 &gt; 63.07-10)</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -928,13 +928,13 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-)</t>
+  </si>
+  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1125,6 +1125,12 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
+    <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (#63.04-.03)</t>
+  </si>
+  <si>
+    <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1132,12 +1138,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (#63.04-.03)</t>
-  </si>
-  <si>
-    <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1156,6 +1156,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (#63.04-.04)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1166,9 +1169,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (#63.04-.04)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1257,15 +1257,15 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2+through+862)</t>
+  </si>
+  <si>
     <t>SN.2  / CQ - N/A</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
-    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2+through+862)</t>
-  </si>
-  <si>
     <t>Observation.value[x]:valueQuantity.comparator</t>
   </si>
   <si>
@@ -1317,13 +1317,13 @@
     <t>Quantity.unit</t>
   </si>
   <si>
+    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; UNITS (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
+  </si>
+  <si>
     <t>(see OBX.6 etc.) / CQ.2</t>
   </si>
   <si>
     <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; UNITS (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.system</t>
@@ -1423,6 +1423,9 @@
     <t>http://va.gov/fhir/ValueSet/VSVFLabInterpretation</t>
   </si>
   <si>
+    <t>852: terminologyMaps using VF_LabInterpretation on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2+through+862)</t>
+  </si>
+  <si>
     <t>&lt; 260245000 |Findings values|</t>
   </si>
   <si>
@@ -1433,9 +1436,6 @@
   </si>
   <si>
     <t>363713009 |Has interpretation|</t>
-  </si>
-  <si>
-    <t>852: terminologyMaps using VF_LabInterpretation on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2+through+862)</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -1457,16 +1457,16 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
+    <t>846: source value from CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (#63.04-.99 &gt; 63.041-.01)</t>
+  </si>
+  <si>
+    <t>Chem.LabPanel.LabPanelComment</t>
+  </si>
+  <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
     <t>subjectOf.observationEvent[code="annotation"].value</t>
-  </si>
-  <si>
-    <t>846: source value from CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (#63.04-.99 &gt; 63.041-.01)</t>
-  </si>
-  <si>
-    <t>Chem.LabPanel.LabPanelComment</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -1546,6 +1546,12 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
+    <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
+  </si>
+  <si>
+    <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
+  </si>
+  <si>
     <t>&lt; 123038009 |Specimen|</t>
   </si>
   <si>
@@ -1556,12 +1562,6 @@
   </si>
   <si>
     <t>704319004 |Inherent in|</t>
-  </si>
-  <si>
-    <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
-  </si>
-  <si>
-    <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
   </si>
   <si>
     <t>Observation.device</t>
@@ -1661,15 +1661,15 @@
 </t>
   </si>
   <si>
+    <t>854: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE LOW (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-1)</t>
+  </si>
+  <si>
     <t>OBX-7</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
   </si>
   <si>
-    <t>854: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE LOW (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-1)</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.high</t>
   </si>
   <si>
@@ -1679,10 +1679,10 @@
     <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
   </si>
   <si>
+    <t>850: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE HIGH (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-2)</t>
+  </si>
+  <si>
     <t>value:IVL_PQ.high</t>
-  </si>
-  <si>
-    <t>850: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE HIGH (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-2)</t>
   </si>
   <si>
     <t>Observation.referenceRange.type</t>
@@ -2265,14 +2265,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="239.078125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="183.43359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="239.078125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="183.43359375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2511,22 +2511,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -3148,13 +3148,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3274,13 +3274,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3400,13 +3400,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3528,13 +3528,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3645,25 +3645,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3778,13 +3778,13 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3904,13 +3904,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4029,16 +4029,16 @@
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>84</v>
@@ -4157,16 +4157,16 @@
         <v>84</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>84</v>
@@ -4285,16 +4285,16 @@
         <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4405,25 +4405,25 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4535,16 +4535,16 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4661,16 +4661,16 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4781,22 +4781,22 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4907,22 +4907,22 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5036,19 +5036,19 @@
         <v>250</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>255</v>
@@ -5168,16 +5168,16 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5298,16 +5298,16 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5417,28 +5417,28 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5550,13 +5550,13 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5676,13 +5676,13 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5795,25 +5795,25 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP28" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5929,16 +5929,16 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -6051,25 +6051,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6183,19 +6183,19 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6305,25 +6305,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6431,25 +6431,25 @@
         <v>339</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6561,28 +6561,28 @@
         <v>339</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AR34" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6687,28 +6687,28 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>356</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>358</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6822,13 +6822,13 @@
         <v>365</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>368</v>
@@ -6942,25 +6942,25 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -7072,25 +7072,25 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -7202,13 +7202,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7328,13 +7328,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7447,25 +7447,25 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP41" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7581,16 +7581,16 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7701,25 +7701,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP43" t="s" s="2">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7833,16 +7833,16 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>416</v>
+        <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7961,16 +7961,16 @@
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>416</v>
+        <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8087,16 +8087,16 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8207,28 +8207,28 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>453</v>
       </c>
       <c r="AQ47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8335,28 +8335,28 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>461</v>
+        <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>462</v>
+        <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>464</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8464,25 +8464,25 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8595,16 +8595,16 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8715,25 +8715,25 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>491</v>
+        <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>492</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>84</v>
+        <v>493</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>495</v>
@@ -8844,25 +8844,25 @@
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
+      <c r="AQ52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -8975,16 +8975,16 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9102,13 +9102,13 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9228,13 +9228,13 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9356,13 +9356,13 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9471,25 +9471,25 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>84</v>
+        <v>526</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>526</v>
+        <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP57" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>84</v>
@@ -9595,25 +9595,25 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>84</v>
+        <v>532</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>526</v>
+        <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>532</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>84</v>
+        <v>527</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -9726,19 +9726,19 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AN59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP59" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9854,19 +9854,19 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AN60" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP60" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9986,13 +9986,13 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10107,16 +10107,16 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>526</v>
+        <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10233,16 +10233,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10359,16 +10359,16 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10487,16 +10487,16 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AP65" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10614,13 +10614,13 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10740,13 +10740,13 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10868,13 +10868,13 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10990,22 +10990,22 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO69" t="s" s="2">
+      <c r="AQ69" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>84</v>
@@ -11118,25 +11118,25 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -11249,16 +11249,16 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11374,16 +11374,16 @@
         <v>84</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>453</v>
@@ -11392,7 +11392,7 @@
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>84</v>
+        <v>454</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11505,16 +11505,16 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AP73" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,10 +791,10 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
-  </si>
-  <si>
-    <t>860: terminologyMaps using VF_DiagnosticReportLabStatus on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.04-.35 &gt; 63.07-10)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+  </si>
+  <si>
+    <t>860: terminologyMaps using VF_LabObservationStatus on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.04-.35 &gt; 63.07-10)</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -2255,7 +2255,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.65234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -825,28 +825,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -857,6 +835,31 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -978,6 +981,12 @@
   </si>
   <si>
     <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -2266,7 +2275,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="239.078125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="183.43359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -5107,7 +5116,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5125,16 +5134,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5159,7 +5168,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5174,10 +5183,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5185,13 +5194,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>256</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5235,7 +5244,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5253,10 +5262,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5304,10 +5313,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5315,14 +5324,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5344,16 +5353,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5381,10 +5390,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5402,7 +5411,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5423,30 +5432,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5567,10 +5576,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5693,10 +5702,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5719,19 +5728,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5780,7 +5789,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5795,7 +5804,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5807,10 +5816,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5821,10 +5830,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5850,16 +5859,16 @@
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5908,7 +5917,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5935,10 +5944,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5949,10 +5958,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5975,19 +5984,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -6036,7 +6045,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6051,25 +6060,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6077,10 +6086,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6103,16 +6112,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6162,7 +6171,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6189,13 +6198,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6203,14 +6212,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6229,19 +6238,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6290,7 +6299,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6311,19 +6320,19 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6331,14 +6340,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6357,19 +6366,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6406,7 +6415,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6416,7 +6425,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6425,10 +6434,10 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6437,19 +6446,19 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6457,16 +6466,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6485,19 +6494,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6546,7 +6555,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6555,31 +6564,31 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6587,10 +6596,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6613,16 +6622,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6672,7 +6681,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6687,10 +6696,10 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6699,13 +6708,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6713,10 +6722,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6739,17 +6748,17 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6798,7 +6807,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6813,25 +6822,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6839,10 +6848,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6865,19 +6874,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6914,7 +6923,7 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
@@ -6924,7 +6933,7 @@
         <v>170</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6933,10 +6942,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6948,30 +6957,30 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
@@ -6993,19 +7002,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -7054,7 +7063,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7063,10 +7072,10 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -7078,27 +7087,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7219,10 +7228,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7345,10 +7354,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7371,19 +7380,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7432,7 +7441,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7447,7 +7456,7 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
@@ -7459,10 +7468,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7473,10 +7482,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7502,20 +7511,20 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="R42" t="s" s="2">
         <v>84</v>
@@ -7539,10 +7548,10 @@
         <v>177</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7560,7 +7569,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7587,10 +7596,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7601,10 +7610,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7630,14 +7639,14 @@
         <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7686,7 +7695,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7701,7 +7710,7 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
@@ -7713,10 +7722,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7727,10 +7736,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7756,14 +7765,14 @@
         <v>108</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7812,7 +7821,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7821,7 +7830,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7839,10 +7848,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7853,10 +7862,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7882,16 +7891,16 @@
         <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7940,7 +7949,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7967,10 +7976,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7981,10 +7990,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8010,16 +8019,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8048,7 +8057,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8066,7 +8075,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8075,7 +8084,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8096,7 +8105,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8107,14 +8116,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8136,16 +8145,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8174,7 +8183,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8192,7 +8201,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8207,7 +8216,7 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -8216,27 +8225,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8259,19 +8268,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8320,7 +8329,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8335,10 +8344,10 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
@@ -8347,10 +8356,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8361,10 +8370,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8390,13 +8399,13 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8422,13 +8431,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8446,7 +8455,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8470,27 +8479,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8516,16 +8525,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8550,13 +8559,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8574,7 +8583,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8601,10 +8610,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8615,10 +8624,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8641,16 +8650,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8700,7 +8709,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8715,36 +8724,36 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8767,16 +8776,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8826,7 +8835,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8850,27 +8859,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8893,19 +8902,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8954,7 +8963,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8966,7 +8975,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8981,10 +8990,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8995,10 +9004,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9119,10 +9128,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9245,14 +9254,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9274,10 +9283,10 @@
         <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -9332,7 +9341,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9373,10 +9382,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9399,13 +9408,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9456,7 +9465,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9465,13 +9474,13 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
@@ -9483,10 +9492,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9497,10 +9506,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9523,13 +9532,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9580,7 +9589,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9589,13 +9598,13 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>84</v>
@@ -9607,10 +9616,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9621,10 +9630,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9650,16 +9659,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9687,10 +9696,10 @@
         <v>118</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9708,7 +9717,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9732,13 +9741,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9749,10 +9758,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9778,16 +9787,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9812,13 +9821,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9836,7 +9845,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9860,13 +9869,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9877,10 +9886,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9903,17 +9912,17 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9962,7 +9971,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9992,7 +10001,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10003,10 +10012,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10032,10 +10041,10 @@
         <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10086,7 +10095,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10113,10 +10122,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10127,10 +10136,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10153,16 +10162,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10212,7 +10221,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10239,10 +10248,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10253,10 +10262,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10279,16 +10288,16 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10338,7 +10347,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10365,10 +10374,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10379,10 +10388,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10405,19 +10414,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10466,7 +10475,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10493,10 +10502,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10507,10 +10516,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10631,10 +10640,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10757,14 +10766,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10786,10 +10795,10 @@
         <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -10844,7 +10853,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10885,10 +10894,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10914,16 +10923,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10948,13 +10957,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10972,7 +10981,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -10996,16 +11005,16 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>84</v>
@@ -11013,10 +11022,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11039,19 +11048,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11100,7 +11109,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11124,27 +11133,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11170,16 +11179,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11207,10 +11216,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11228,7 +11237,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11237,7 +11246,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11258,7 +11267,7 @@
         <v>137</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11269,14 +11278,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11298,16 +11307,16 @@
         <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11335,10 +11344,10 @@
         <v>188</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11356,7 +11365,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11380,27 +11389,27 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11426,16 +11435,16 @@
         <v>85</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11484,7 +11493,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11511,10 +11520,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (63.04) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>851: source value from CHEM, HEM, TOX, RIA, SER, etc. - IEN (#63.04-.001)</t>
+    <t>851: source value from CHEM, HEM, TOX, RIA, SER, etc. - IEN (63.04-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -794,7 +794,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
   </si>
   <si>
-    <t>860: terminologyMaps using VF_LabObservationStatus on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.04-.35 &gt; 63.07-10)</t>
+    <t>860: terminologyMaps using VF_LabObservationStatus on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (63.04-.35 &gt; 63.07-10)</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -931,7 +931,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-)</t>
+    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-)</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -983,7 +983,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1112,7 +1112,7 @@
 </t>
   </si>
   <si>
-    <t>845: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE/TIME SPECIMEN TAKEN (#63.04-.01)</t>
+    <t>845: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE/TIME SPECIMEN TAKEN (63.04-.01)</t>
   </si>
   <si>
     <t>Chem.LabChem.LabChemSpecimenDateTime,Chem.LabPanel.LabChemSpecimenDateTime,Chem.OrderedLabPanel.LabChemSpecimenDateTime,Chem.PatientLabChem.LabChemSpecimenDateTime</t>
@@ -1134,7 +1134,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (#63.04-.03)</t>
+    <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (63.04-.03)</t>
   </si>
   <si>
     <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
@@ -1165,7 +1165,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (#63.04-.04)</t>
+    <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (63.04-.04)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1266,7 +1266,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2+through+862)</t>
+    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (63.04-2+through+862)</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -1326,7 +1326,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; UNITS (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
+    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; UNITS (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
   </si>
   <si>
     <t>(see OBX.6 etc.) / CQ.2</t>
@@ -1432,7 +1432,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFLabInterpretation</t>
   </si>
   <si>
-    <t>852: terminologyMaps using VF_LabInterpretation on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2+through+862)</t>
+    <t>852: terminologyMaps using VF_LabInterpretation on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (63.04-2+through+862)</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1466,7 +1466,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>846: source value from CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (#63.04-.99 &gt; 63.041-.01)</t>
+    <t>846: source value from CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (63.04-.99 &gt; 63.041-.01)</t>
   </si>
   <si>
     <t>Chem.LabPanel.LabPanelComment</t>
@@ -1555,7 +1555,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
+    <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (63.04-.06)</t>
   </si>
   <si>
     <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
@@ -1670,7 +1670,7 @@
 </t>
   </si>
   <si>
-    <t>854: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE LOW (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-1)</t>
+    <t>854: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE LOW (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-1)</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1688,7 +1688,7 @@
     <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
   </si>
   <si>
-    <t>850: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE HIGH (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-2)</t>
+    <t>850: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE HIGH (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-2)</t>
   </si>
   <si>
     <t>value:IVL_PQ.high</t>
@@ -2274,7 +2274,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="239.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="235.20703125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1326,7 +1326,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; UNITS (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
+    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN-UNITS (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
   </si>
   <si>
     <t>(see OBX.6 etc.) / CQ.2</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1326,7 +1326,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN-UNITS (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
+    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - UNITS (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
   </si>
   <si>
     <t>(see OBX.6 etc.) / CQ.2</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1266,7 +1266,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (63.04-2+through+862)</t>
+    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - testnames (63.04-2+through+862)</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -1432,7 +1432,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFLabInterpretation</t>
   </si>
   <si>
-    <t>852: terminologyMaps using VF_LabInterpretation on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (63.04-2+through+862)</t>
+    <t>852: terminologyMaps using VF_LabInterpretation on CHEM, HEM, TOX, RIA, SER, etc. - testnames (63.04-2+through+862)</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="610">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -986,7 +986,7 @@
     <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1166,6 +1166,9 @@
   </si>
   <si>
     <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (63.04-.04)</t>
+  </si>
+  <si>
+    <t>Chem.LabChem.AccessionInstitutionIEN,Chem.PatientLabChem.AccessionInstitutionIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -6825,22 +6828,22 @@
         <v>367</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6848,10 +6851,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6874,19 +6877,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6933,7 +6936,7 @@
         <v>170</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6942,10 +6945,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6957,30 +6960,30 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
@@ -7002,19 +7005,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -7063,7 +7066,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7072,10 +7075,10 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -7087,27 +7090,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7228,10 +7231,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7354,10 +7357,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7380,19 +7383,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7441,7 +7444,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7456,7 +7459,7 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
@@ -7468,10 +7471,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7482,10 +7485,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7511,20 +7514,20 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="R42" t="s" s="2">
         <v>84</v>
@@ -7548,10 +7551,10 @@
         <v>177</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7569,7 +7572,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7596,10 +7599,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7610,10 +7613,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7639,14 +7642,14 @@
         <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7695,7 +7698,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7710,7 +7713,7 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
@@ -7722,10 +7725,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7736,10 +7739,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7765,14 +7768,14 @@
         <v>108</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7821,7 +7824,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7830,7 +7833,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7848,10 +7851,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7862,10 +7865,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7891,16 +7894,16 @@
         <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7949,7 +7952,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7976,10 +7979,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7990,10 +7993,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8019,16 +8022,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8057,7 +8060,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8075,7 +8078,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8084,7 +8087,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8105,7 +8108,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8116,14 +8119,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8145,16 +8148,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8183,7 +8186,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8201,7 +8204,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8216,7 +8219,7 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -8225,27 +8228,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8268,19 +8271,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8329,7 +8332,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8344,10 +8347,10 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
@@ -8356,10 +8359,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8370,10 +8373,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8399,13 +8402,13 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8431,13 +8434,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8455,7 +8458,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8479,27 +8482,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8525,16 +8528,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8559,13 +8562,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8583,7 +8586,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8610,10 +8613,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8624,10 +8627,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8650,16 +8653,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8709,7 +8712,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8724,36 +8727,36 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8776,16 +8779,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8835,7 +8838,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8859,27 +8862,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8902,19 +8905,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8963,7 +8966,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8975,7 +8978,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8990,10 +8993,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9004,10 +9007,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9128,10 +9131,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9254,14 +9257,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9283,10 +9286,10 @@
         <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -9341,7 +9344,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9382,10 +9385,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9408,13 +9411,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9465,7 +9468,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9474,13 +9477,13 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
@@ -9492,10 +9495,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9506,10 +9509,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9532,13 +9535,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9589,7 +9592,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9598,13 +9601,13 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>84</v>
@@ -9616,10 +9619,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9630,10 +9633,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9659,16 +9662,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9696,10 +9699,10 @@
         <v>118</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9717,7 +9720,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9741,13 +9744,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9758,10 +9761,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9787,16 +9790,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9821,13 +9824,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9845,7 +9848,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9869,13 +9872,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9886,10 +9889,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9912,17 +9915,17 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9971,7 +9974,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10001,7 +10004,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10012,10 +10015,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10041,10 +10044,10 @@
         <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10095,7 +10098,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10122,10 +10125,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10136,10 +10139,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10162,16 +10165,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10221,7 +10224,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10248,10 +10251,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10262,10 +10265,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10288,16 +10291,16 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10347,7 +10350,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10374,10 +10377,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10388,10 +10391,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10414,19 +10417,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10475,7 +10478,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10502,10 +10505,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10516,10 +10519,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10640,10 +10643,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10766,14 +10769,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10795,10 +10798,10 @@
         <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -10853,7 +10856,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10894,10 +10897,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10923,13 +10926,13 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>275</v>
@@ -10957,10 +10960,10 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>277</v>
@@ -10981,7 +10984,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -11005,7 +11008,7 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>280</v>
@@ -11022,10 +11025,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11048,19 +11051,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11109,7 +11112,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11133,27 +11136,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11179,16 +11182,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11216,10 +11219,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11237,7 +11240,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11246,7 +11249,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11267,7 +11270,7 @@
         <v>137</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11278,14 +11281,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11307,16 +11310,16 @@
         <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11344,28 +11347,28 @@
         <v>188</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11389,27 +11392,27 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11435,16 +11438,16 @@
         <v>85</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11493,7 +11496,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11520,10 +11523,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,10 +632,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>851-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -938,6 +944,139 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>853-1: fixed value = http://loinc.org</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>853-2: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01)</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>853-3: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1)</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -2239,7 +2378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR73"/>
+  <dimension ref="A1:AR80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
@@ -2277,7 +2416,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="235.20703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="251.90234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -4206,7 +4345,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -4237,10 +4376,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -4276,7 +4415,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4291,7 +4430,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4303,10 +4442,10 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4317,10 +4456,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4346,13 +4485,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4366,7 +4505,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4402,7 +4541,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4417,7 +4556,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -4429,10 +4568,10 @@
         <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4443,10 +4582,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4469,13 +4608,13 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4526,7 +4665,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4553,10 +4692,10 @@
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4567,10 +4706,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4593,16 +4732,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4652,7 +4791,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4679,10 +4818,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4693,14 +4832,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4719,17 +4858,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4778,7 +4917,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4799,16 +4938,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4819,14 +4958,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4845,16 +4984,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4904,7 +5043,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4925,16 +5064,16 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4945,10 +5084,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4974,16 +5113,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -5012,7 +5151,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -5030,7 +5169,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>94</v>
@@ -5045,25 +5184,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -5071,10 +5210,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5100,16 +5239,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5119,7 +5258,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5137,16 +5276,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5156,7 +5295,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5171,7 +5310,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5186,10 +5325,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5197,13 +5336,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5228,16 +5367,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5247,7 +5386,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5265,10 +5404,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5286,7 +5425,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5316,10 +5455,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5327,14 +5466,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5356,16 +5495,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5393,10 +5532,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5414,7 +5553,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5435,30 +5574,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5579,10 +5718,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5705,10 +5844,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5731,19 +5870,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5792,7 +5931,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5807,7 +5946,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5819,10 +5958,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5833,10 +5972,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5856,23 +5995,19 @@
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>162</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
       </c>
@@ -5920,7 +6055,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5932,7 +6067,7 @@
         <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5947,10 +6082,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>303</v>
+        <v>165</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5961,46 +6096,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>167</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6036,52 +6169,52 @@
         <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>171</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>313</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>314</v>
+        <v>165</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6089,10 +6222,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6103,10 +6236,10 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6115,18 +6248,20 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6135,7 +6270,7 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>84</v>
@@ -6174,13 +6309,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6189,7 +6324,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6201,13 +6336,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6215,14 +6350,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>323</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6241,20 +6376,18 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>324</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>84</v>
       </c>
@@ -6302,7 +6435,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6323,19 +6456,19 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>332</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6343,14 +6476,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6369,19 +6502,17 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>335</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6418,17 +6549,19 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6437,31 +6570,31 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6469,16 +6602,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6497,19 +6628,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>349</v>
+        <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6558,7 +6687,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6567,31 +6696,31 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6599,10 +6728,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6616,7 +6745,7 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
@@ -6625,18 +6754,20 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6684,7 +6815,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6699,10 +6830,10 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>358</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6711,13 +6842,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>361</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6725,10 +6856,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6739,10 +6870,10 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -6751,17 +6882,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>363</v>
+        <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6810,13 +6943,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -6825,25 +6958,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>367</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>372</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6851,10 +6984,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6862,7 +6995,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6877,19 +7010,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6926,17 +7059,19 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6945,46 +7080,44 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>380</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6993,10 +7126,10 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
@@ -7005,20 +7138,18 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7066,19 +7197,19 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>380</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -7090,31 +7221,31 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>382</v>
+        <v>282</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7130,19 +7261,23 @@
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>161</v>
+        <v>370</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7190,7 +7325,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7202,7 +7337,7 @@
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7211,19 +7346,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>165</v>
+        <v>377</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>378</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7231,44 +7366,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>139</v>
+        <v>380</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>140</v>
+        <v>381</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>141</v>
+        <v>382</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>167</v>
+        <v>383</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7304,11 +7441,9 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7316,19 +7451,19 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>388</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7337,19 +7472,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>165</v>
+        <v>391</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>392</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7357,14 +7492,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7383,19 +7520,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7444,7 +7581,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7453,31 +7590,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>388</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>392</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7485,10 +7622,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7502,33 +7639,31 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>114</v>
+        <v>399</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q42" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7548,13 +7683,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7572,7 +7707,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7587,10 +7722,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7599,13 +7734,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7613,10 +7748,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7627,7 +7762,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>95</v>
@@ -7639,17 +7774,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>161</v>
+        <v>409</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7698,13 +7833,13 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7713,25 +7848,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7739,10 +7874,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7756,7 +7891,7 @@
         <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
@@ -7765,17 +7900,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>108</v>
+        <v>420</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7812,19 +7949,17 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7833,34 +7968,34 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7868,9 +8003,11 @@
         <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7882,7 +8019,7 @@
         <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
@@ -7891,19 +8028,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>433</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7952,7 +8089,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7961,10 +8098,10 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>425</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>426</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7976,27 +8113,27 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>427</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8010,7 +8147,7 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -8019,20 +8156,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>162</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8056,11 +8189,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8078,7 +8213,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>164</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8087,10 +8222,10 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -8105,10 +8240,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>446</v>
+        <v>165</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8119,14 +8254,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>448</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8136,7 +8271,7 @@
         <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>84</v>
@@ -8145,20 +8280,18 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>449</v>
+        <v>141</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8182,29 +8315,31 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>447</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8216,10 +8351,10 @@
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>454</v>
+        <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
@@ -8228,27 +8363,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>457</v>
+        <v>165</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8259,7 +8394,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>95</v>
@@ -8268,22 +8403,22 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8332,13 +8467,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8347,10 +8482,10 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
@@ -8359,10 +8494,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8373,10 +8508,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8393,28 +8528,30 @@
         <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="R49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8434,13 +8571,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>473</v>
+        <v>177</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8458,7 +8595,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8482,27 +8619,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8516,28 +8653,26 @@
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8562,13 +8697,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>473</v>
+        <v>84</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8586,7 +8721,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8601,7 +8736,7 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>466</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
@@ -8613,10 +8748,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8627,10 +8762,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8644,27 +8779,27 @@
         <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K51" t="s" s="2">
-        <v>490</v>
+        <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8712,7 +8847,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8721,42 +8856,42 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>475</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>495</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>499</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8776,21 +8911,23 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>501</v>
+        <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8838,7 +8975,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8862,27 +8999,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>505</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>506</v>
+        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>508</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8893,10 +9030,10 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
@@ -8905,19 +9042,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>510</v>
+        <v>183</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>514</v>
+        <v>489</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8942,13 +9079,11 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -8966,19 +9101,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>84</v>
+        <v>491</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>515</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8993,10 +9128,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>516</v>
+        <v>137</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9007,24 +9142,24 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>494</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>84</v>
@@ -9033,16 +9168,20 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>162</v>
+        <v>495</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9066,13 +9205,11 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>84</v>
+        <v>499</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9090,22 +9227,22 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>84</v>
+        <v>500</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>84</v>
@@ -9114,31 +9251,31 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>84</v>
+        <v>501</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>84</v>
+        <v>502</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>165</v>
+        <v>503</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>84</v>
+        <v>504</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9148,7 +9285,7 @@
         <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>84</v>
@@ -9157,18 +9294,20 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>140</v>
+        <v>506</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>141</v>
+        <v>507</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>167</v>
+        <v>508</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9216,7 +9355,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>171</v>
+        <v>505</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9228,13 +9367,13 @@
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>84</v>
+        <v>511</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>84</v>
+        <v>512</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>84</v>
@@ -9243,10 +9382,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>84</v>
+        <v>513</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>165</v>
+        <v>514</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9257,46 +9396,44 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9320,13 +9457,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9344,51 +9481,51 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>84</v>
+        <v>525</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9402,7 +9539,7 @@
         <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>84</v>
@@ -9411,7 +9548,7 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>526</v>
+        <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>527</v>
@@ -9419,8 +9556,12 @@
       <c r="M57" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="N57" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9444,13 +9585,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>84</v>
+        <v>531</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>84</v>
+        <v>532</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9468,7 +9609,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9477,13 +9618,13 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>529</v>
+        <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>530</v>
+        <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
@@ -9495,10 +9636,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9509,10 +9650,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9535,15 +9676,17 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9592,7 +9735,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9601,42 +9744,42 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>529</v>
+        <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>84</v>
+        <v>542</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>84</v>
+        <v>545</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9659,20 +9802,18 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>183</v>
+        <v>547</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9696,13 +9837,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>543</v>
+        <v>84</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>544</v>
+        <v>84</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9720,7 +9861,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9744,27 +9885,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>457</v>
+        <v>553</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9787,19 +9928,19 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>183</v>
+        <v>556</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9824,13 +9965,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>473</v>
+        <v>84</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>552</v>
+        <v>84</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>553</v>
+        <v>84</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9848,7 +9989,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9860,7 +10001,7 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>561</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -9872,13 +10013,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>545</v>
+        <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>457</v>
+        <v>563</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9889,10 +10030,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9915,18 +10056,16 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>555</v>
+        <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>556</v>
+        <v>162</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>557</v>
+        <v>163</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>558</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9974,7 +10113,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>554</v>
+        <v>164</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9986,7 +10125,7 @@
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -10004,7 +10143,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>559</v>
+        <v>165</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10015,21 +10154,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -10041,15 +10180,17 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10098,19 +10239,19 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>560</v>
+        <v>171</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
@@ -10125,10 +10266,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>531</v>
+        <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>563</v>
+        <v>165</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10139,14 +10280,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10159,24 +10300,26 @@
         <v>84</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>565</v>
+        <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10224,7 +10367,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10236,7 +10379,7 @@
         <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>84</v>
@@ -10251,10 +10394,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>570</v>
+        <v>137</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10279,16 +10422,16 @@
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>572</v>
@@ -10299,9 +10442,7 @@
       <c r="M64" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>575</v>
-      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10356,16 +10497,16 @@
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>84</v>
+        <v>576</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>84</v>
@@ -10377,10 +10518,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10391,10 +10532,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10405,32 +10546,28 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>510</v>
+        <v>572</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O65" t="s" s="2">
         <v>581</v>
       </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10478,22 +10615,22 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>84</v>
@@ -10505,7 +10642,7 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>583</v>
@@ -10545,16 +10682,20 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>162</v>
+        <v>585</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10578,13 +10719,13 @@
         <v>84</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -10602,7 +10743,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>164</v>
+        <v>584</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10614,7 +10755,7 @@
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10626,13 +10767,13 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>84</v>
+        <v>592</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>165</v>
+        <v>503</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10643,14 +10784,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10669,18 +10810,20 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>141</v>
+        <v>594</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>167</v>
+        <v>595</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10704,13 +10847,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>84</v>
+        <v>598</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10728,7 +10871,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>171</v>
+        <v>593</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10740,7 +10883,7 @@
         <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10752,13 +10895,13 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>84</v>
+        <v>592</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>165</v>
+        <v>503</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10769,45 +10912,43 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>140</v>
+        <v>601</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>522</v>
+        <v>602</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>149</v>
+        <v>604</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10856,19 +10997,19 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>524</v>
+        <v>600</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -10886,7 +11027,7 @@
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>137</v>
+        <v>605</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10897,10 +11038,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10908,7 +11049,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>94</v>
@@ -10920,23 +11061,19 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10960,13 +11097,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>473</v>
+        <v>84</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>591</v>
+        <v>84</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10984,10 +11121,10 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>94</v>
@@ -11008,16 +11145,16 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>592</v>
+        <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>280</v>
+        <v>577</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>281</v>
+        <v>609</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>84</v>
@@ -11025,10 +11162,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11039,7 +11176,7 @@
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>84</v>
@@ -11051,20 +11188,18 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>374</v>
+        <v>611</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>84</v>
       </c>
@@ -11112,13 +11247,13 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>84</v>
@@ -11136,27 +11271,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>597</v>
+        <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>382</v>
+        <v>615</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>383</v>
+        <v>616</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11167,7 +11302,7 @@
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11176,23 +11311,21 @@
         <v>84</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>183</v>
+        <v>618</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11216,13 +11349,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>602</v>
+        <v>84</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11240,16 +11373,16 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>603</v>
+        <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11267,10 +11400,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>137</v>
+        <v>615</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>446</v>
+        <v>622</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11281,14 +11414,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11304,22 +11437,22 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>183</v>
+        <v>556</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>449</v>
+        <v>624</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>450</v>
+        <v>625</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>451</v>
+        <v>626</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>452</v>
+        <v>627</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11344,13 +11477,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>605</v>
+        <v>84</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>606</v>
+        <v>84</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11368,7 +11501,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11392,27 +11525,27 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>456</v>
+        <v>628</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>457</v>
+        <v>629</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11423,7 +11556,7 @@
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
@@ -11435,20 +11568,16 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>608</v>
+        <v>162</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11496,47 +11625,941 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>607</v>
+        <v>164</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G74" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AI73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
+      <c r="H74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR73" t="s" s="2">
+      <c r="AK76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR80" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR73">
+  <autoFilter ref="A1:AR80">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11546,7 +12569,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/63.04</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>851-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>851-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/63.04</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/63.04</t>
+    <t>http://va.gov/identifiers/$Sta3n/63.04</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>851-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/63.04</t>
+    <t>851-1: fixed value = http://va.gov/identifiers/$Sta3n/63.04</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
